--- a/dataset.xlsx
+++ b/dataset.xlsx
@@ -1379,7 +1379,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1390,12 +1390,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF780373"/>
-        <bgColor rgb="FF800080"/>
       </patternFill>
     </fill>
   </fills>
@@ -1433,7 +1427,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1450,10 +1444,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1463,66 +1453,6 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF780373"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -18105,7 +18035,7 @@
       <c r="B16" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="3" t="s">
         <v>390</v>
       </c>
       <c r="D16" s="1" t="n">
@@ -23545,7 +23475,7 @@
       <c r="B21" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="3" t="s">
         <v>400</v>
       </c>
       <c r="D21" s="1" t="n">
@@ -24633,7 +24563,7 @@
       <c r="B22" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="3" t="s">
         <v>402</v>
       </c>
       <c r="D22" s="1" t="n">
@@ -25721,7 +25651,7 @@
       <c r="B23" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="3" t="s">
         <v>404</v>
       </c>
       <c r="D23" s="1" t="n">
@@ -26809,7 +26739,7 @@
       <c r="B24" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="3" t="s">
         <v>406</v>
       </c>
       <c r="D24" s="1" t="n">
@@ -27897,7 +27827,7 @@
       <c r="B25" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="3" t="s">
         <v>408</v>
       </c>
       <c r="D25" s="1" t="n">
@@ -28985,7 +28915,7 @@
       <c r="B26" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="3" t="s">
         <v>410</v>
       </c>
       <c r="D26" s="1" t="n">
@@ -30073,7 +30003,7 @@
       <c r="B27" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="3" t="s">
         <v>412</v>
       </c>
       <c r="D27" s="1" t="n">
@@ -31154,14 +31084,14 @@
         <v>-0.05313</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="n">
         <v>26</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="3" t="s">
         <v>414</v>
       </c>
       <c r="D28" s="1" t="n">
@@ -32249,7 +32179,7 @@
       <c r="B29" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="3" t="s">
         <v>362</v>
       </c>
       <c r="D29" s="1" t="n">
@@ -33337,7 +33267,7 @@
       <c r="B30" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="3" t="s">
         <v>364</v>
       </c>
       <c r="D30" s="1" t="n">
@@ -34425,7 +34355,7 @@
       <c r="B31" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="3" t="s">
         <v>366</v>
       </c>
       <c r="D31" s="1" t="n">
@@ -35513,7 +35443,7 @@
       <c r="B32" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="3" t="s">
         <v>368</v>
       </c>
       <c r="D32" s="1" t="n">
@@ -36601,7 +36531,7 @@
       <c r="B33" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="3" t="s">
         <v>370</v>
       </c>
       <c r="D33" s="1" t="n">
@@ -37689,7 +37619,7 @@
       <c r="B34" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="3" t="s">
         <v>372</v>
       </c>
       <c r="D34" s="1" t="n">
@@ -38777,7 +38707,7 @@
       <c r="B35" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="3" t="s">
         <v>374</v>
       </c>
       <c r="D35" s="1" t="n">
@@ -39865,7 +39795,7 @@
       <c r="B36" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="3" t="s">
         <v>376</v>
       </c>
       <c r="D36" s="1" t="n">
@@ -40953,7 +40883,7 @@
       <c r="B37" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="3" t="s">
         <v>378</v>
       </c>
       <c r="D37" s="1" t="n">
@@ -42041,7 +41971,7 @@
       <c r="B38" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="3" t="s">
         <v>380</v>
       </c>
       <c r="D38" s="1" t="n">
@@ -43129,7 +43059,7 @@
       <c r="B39" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="3" t="s">
         <v>384</v>
       </c>
       <c r="D39" s="1" t="n">
@@ -44217,7 +44147,7 @@
       <c r="B40" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="3" t="s">
         <v>386</v>
       </c>
       <c r="D40" s="1" t="n">
@@ -45305,7 +45235,7 @@
       <c r="B41" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="3" t="s">
         <v>388</v>
       </c>
       <c r="D41" s="1" t="n">
@@ -46393,7 +46323,7 @@
       <c r="B42" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="3" t="s">
         <v>392</v>
       </c>
       <c r="D42" s="1" t="n">
@@ -47481,7 +47411,7 @@
       <c r="B43" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="3" t="s">
         <v>394</v>
       </c>
       <c r="D43" s="1" t="n">
@@ -48569,7 +48499,7 @@
       <c r="B44" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="3" t="s">
         <v>396</v>
       </c>
       <c r="D44" s="1" t="n">
@@ -49657,7 +49587,7 @@
       <c r="B45" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="3" t="s">
         <v>398</v>
       </c>
       <c r="D45" s="1" t="n">
@@ -50745,7 +50675,7 @@
       <c r="B46" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="3" t="s">
         <v>400</v>
       </c>
       <c r="D46" s="1" t="n">
@@ -51833,7 +51763,7 @@
       <c r="B47" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="3" t="s">
         <v>402</v>
       </c>
       <c r="D47" s="1" t="n">
@@ -52921,7 +52851,7 @@
       <c r="B48" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="3" t="s">
         <v>404</v>
       </c>
       <c r="D48" s="1" t="n">
@@ -54009,7 +53939,7 @@
       <c r="B49" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="3" t="s">
         <v>406</v>
       </c>
       <c r="D49" s="1" t="n">
@@ -55097,7 +55027,7 @@
       <c r="B50" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="3" t="s">
         <v>408</v>
       </c>
       <c r="D50" s="1" t="n">
@@ -56185,7 +56115,7 @@
       <c r="B51" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="3" t="s">
         <v>410</v>
       </c>
       <c r="D51" s="1" t="n">
@@ -57273,7 +57203,7 @@
       <c r="B52" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="3" t="s">
         <v>412</v>
       </c>
       <c r="D52" s="1" t="n">
@@ -58361,7 +58291,7 @@
       <c r="B53" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" s="3" t="s">
         <v>414</v>
       </c>
       <c r="D53" s="1" t="n">
